--- a/data/trans_orig/P1412-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2012</t>
+          <t>Población con diagnóstico de angina de pecho en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>991</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4977</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4974</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5297</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425253</t>
+          <t>425260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879079</t>
+          <t>879402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,62 +1110,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5979</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6686</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>682153</t>
+          <t>681953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609308</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1289709</t>
+          <t>1290416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,97 +1418,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5915</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5623</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5642</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>679855</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>681863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703659</t>
+          <t>704018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1385795</t>
+          <t>1385814</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,62 +1796,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2188</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6432</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2078</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6904</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607202</t>
+          <t>606787</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>612076</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>614264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1221976</t>
+          <t>1222448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424242</t>
+          <t>424314</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>438224</t>
+          <t>438174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446754</t>
+          <t>446756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>866759</t>
+          <t>865106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875254</t>
+          <t>875244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291972</t>
+          <t>290785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305749</t>
+          <t>306532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>345171</t>
+          <t>344967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>353023</t>
+          <t>353022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>641669</t>
+          <t>641945</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>657765</t>
+          <t>657832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>37041</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232109</t>
+          <t>231293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244644</t>
+          <t>244735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>361971</t>
+          <t>361224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378735</t>
+          <t>378863</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>599164</t>
+          <t>600606</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>620306</t>
+          <t>620346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>34907</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37435</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63667</t>
+          <t>64582</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3391318</t>
+          <t>3391872</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3411825</t>
+          <t>3412764</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3515533</t>
+          <t>3515915</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3536417</t>
+          <t>3536864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6916080</t>
+          <t>6915165</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6945203</t>
+          <t>6944769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2016</t>
+          <t>Población con diagnóstico de angina de pecho en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,97 +3711,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7870</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2044</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6827</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7133</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8888</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388622</t>
+          <t>387885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>806330</t>
+          <t>808391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,62 +4089,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>8081</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2253</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7496</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583285</t>
+          <t>581905</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1146544</t>
+          <t>1145959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4397,97 +4397,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4718</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>940</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4717</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5630</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5290</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656669</t>
+          <t>656668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1325193</t>
+          <t>1324853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,97 +4740,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>643920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>646048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>647010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>649077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1293026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1295125</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461352</t>
+          <t>461506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474588</t>
+          <t>473686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>487227</t>
+          <t>486268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495691</t>
+          <t>495688</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>953113</t>
+          <t>953538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>969076</t>
+          <t>968154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>22633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318888</t>
+          <t>318494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331267</t>
+          <t>330498</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>366660</t>
+          <t>366457</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375759</t>
+          <t>375765</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>689726</t>
+          <t>689459</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>705735</t>
+          <t>705186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>16390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24065</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243896</t>
+          <t>243885</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253726</t>
+          <t>253718</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386210</t>
+          <t>383779</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397606</t>
+          <t>396534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>633102</t>
+          <t>632485</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649033</t>
+          <t>649021</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29579</t>
+          <t>30233</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60229</t>
+          <t>60484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3355101</t>
+          <t>3357025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3377316</t>
+          <t>3377507</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3514963</t>
+          <t>3514309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3533449</t>
+          <t>3534000</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6878663</t>
+          <t>6878408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6905651</t>
+          <t>6905506</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2023</t>
+          <t>Población con diagnóstico de angina de pecho en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,97 +6690,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3603</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310311</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709584</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7033,97 +7033,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2683</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509374</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>932698</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528580</t>
+          <t>528393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537155</t>
+          <t>537465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1068145</t>
+          <t>1068897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13445</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874341</t>
+          <t>873291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886408</t>
+          <t>886375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>705558</t>
+          <t>706213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>711021</t>
+          <t>711000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1584378</t>
+          <t>1582854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1596527</t>
+          <t>1596304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>550051</t>
+          <t>549468</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>558482</t>
+          <t>558534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>535015</t>
+          <t>535597</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>542249</t>
+          <t>542351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089205</t>
+          <t>1089338</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1099632</t>
+          <t>1099937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15552</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>351895</t>
+          <t>352731</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362370</t>
+          <t>362263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>599772</t>
+          <t>599303</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607488</t>
+          <t>607148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>955107</t>
+          <t>955006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>969986</t>
+          <t>969760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>266843</t>
+          <t>266008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276596</t>
+          <t>276641</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>415146</t>
+          <t>415540</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>422024</t>
+          <t>422125</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>685470</t>
+          <t>685411</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>697113</t>
+          <t>696846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60742</t>
+          <t>60708</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3413847</t>
+          <t>3412896</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3434693</t>
+          <t>3434225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3630420</t>
+          <t>3630596</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3643400</t>
+          <t>3643542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7050632</t>
+          <t>7050666</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7075527</t>
+          <t>7075167</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1412-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425260</t>
+          <t>425220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879402</t>
+          <t>880375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681953</t>
+          <t>682120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1290416</t>
+          <t>1291218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>704018</t>
+          <t>702650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1385814</t>
+          <t>1385774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606787</t>
+          <t>607995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1222448</t>
+          <t>1221974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424314</t>
+          <t>424775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>438174</t>
+          <t>438508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446756</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865106</t>
+          <t>865921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875244</t>
+          <t>875252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>16936</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>21067</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290785</t>
+          <t>292850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306532</t>
+          <t>306254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344967</t>
+          <t>346058</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>353022</t>
+          <t>353019</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>641945</t>
+          <t>642715</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>657832</t>
+          <t>657788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>26177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231293</t>
+          <t>231927</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244735</t>
+          <t>244448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>361224</t>
+          <t>361619</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378863</t>
+          <t>379020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>600606</t>
+          <t>599519</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>620346</t>
+          <t>621285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34907</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37053</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34978</t>
+          <t>35976</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>65540</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3391872</t>
+          <t>3392539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3412764</t>
+          <t>3412587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3515915</t>
+          <t>3516221</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3536864</t>
+          <t>3536881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6915165</t>
+          <t>6914207</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6944769</t>
+          <t>6943771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387885</t>
+          <t>388611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808391</t>
+          <t>808135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581905</t>
+          <t>582983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145959</t>
+          <t>1146901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656668</t>
+          <t>655032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1324853</t>
+          <t>1325103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461506</t>
+          <t>461978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473686</t>
+          <t>473750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486268</t>
+          <t>487317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495688</t>
+          <t>495690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>953538</t>
+          <t>954209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968154</t>
+          <t>968354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22633</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318494</t>
+          <t>318657</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330498</t>
+          <t>331255</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>366457</t>
+          <t>366047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375765</t>
+          <t>375745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>689459</t>
+          <t>690058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>705186</t>
+          <t>704810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243885</t>
+          <t>243834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253718</t>
+          <t>253701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383779</t>
+          <t>385131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396534</t>
+          <t>397639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>632485</t>
+          <t>633104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649021</t>
+          <t>648824</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37325</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>31245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60484</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3357025</t>
+          <t>3356275</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3377507</t>
+          <t>3377392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3514309</t>
+          <t>3513863</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3534000</t>
+          <t>3533417</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6878408</t>
+          <t>6879056</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6905506</t>
+          <t>6907647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -7484,22 +7484,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>532634</t>
+          <t>616942</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528393</t>
+          <t>611991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533659</t>
+          <t>618083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -7519,17 +7519,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>540388</t>
+          <t>619991</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537465</t>
+          <t>617612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541112</t>
+          <t>620778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1073021</t>
+          <t>1236932</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1068897</t>
+          <t>1231290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074771</t>
+          <t>1238860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533659</t>
+          <t>618083</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533659</t>
+          <t>618083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533659</t>
+          <t>618083</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541112</t>
+          <t>620778</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541112</t>
+          <t>620778</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541112</t>
+          <t>620778</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1074771</t>
+          <t>1238860</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1074771</t>
+          <t>1238860</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1074771</t>
+          <t>1238860</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,17 +7749,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>882210</t>
+          <t>694845</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873291</t>
+          <t>687657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886375</t>
+          <t>698623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,17 +7862,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>709679</t>
+          <t>733068</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706213</t>
+          <t>729123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>711000</t>
+          <t>734453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1591889</t>
+          <t>1427913</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1582854</t>
+          <t>1417711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1596304</t>
+          <t>1431942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711608</t>
+          <t>735064</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711608</t>
+          <t>735064</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711608</t>
+          <t>735064</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599394</t>
+          <t>1435682</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599394</t>
+          <t>1435682</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599394</t>
+          <t>1435682</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10769</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,17 +8127,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>17299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>555752</t>
+          <t>603868</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>549468</t>
+          <t>598039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>558534</t>
+          <t>606631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>539625</t>
+          <t>600635</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>535597</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>542351</t>
+          <t>604005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,17 +8240,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1095376</t>
+          <t>1204503</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089338</t>
+          <t>1197825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1099937</t>
+          <t>1209043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>358418</t>
+          <t>396726</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352731</t>
+          <t>390291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362263</t>
+          <t>400795</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>604193</t>
+          <t>434176</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>599303</t>
+          <t>430211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607148</t>
+          <t>436822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>962610</t>
+          <t>830903</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>955006</t>
+          <t>824213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>969760</t>
+          <t>836005</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>18850</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22780</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>272721</t>
+          <t>298416</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>266008</t>
+          <t>291711</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276641</t>
+          <t>302971</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>419433</t>
+          <t>457141</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>415540</t>
+          <t>452753</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>422125</t>
+          <t>460091</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>692154</t>
+          <t>755557</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>685411</t>
+          <t>748285</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>696846</t>
+          <t>761537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42526</t>
+          <t>45421</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>67365</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3425269</t>
+          <t>3495481</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3412896</t>
+          <t>3482731</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3434225</t>
+          <t>3504176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3638022</t>
+          <t>3708605</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3630596</t>
+          <t>3701428</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3643542</t>
+          <t>3714849</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7063291</t>
+          <t>7204086</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7050666</t>
+          <t>7190364</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7075167</t>
+          <t>7215168</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
